--- a/SGC-CKN/Excel/4f826b0d-57fe-4042-8073-c23288e8fd60_Thanh_Hoá_P1-46_D800_09-04-2026.xlsx
+++ b/SGC-CKN/Excel/4f826b0d-57fe-4042-8073-c23288e8fd60_Thanh_Hoá_P1-46_D800_09-04-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>19:10 08/04/2026</t>
+    <t>19:20 08/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>21:43 09/04/2026</t>
+    <t>02:43 09/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
